--- a/docs/reports/ER_Kavach_Unified_KPI_Jun8-Jun14.xlsx
+++ b/docs/reports/ER_Kavach_Unified_KPI_Jun8-Jun14.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="170" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="171" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -282,6 +282,12 @@
       <color rgb="FF9C0006"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="40">
@@ -789,7 +795,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -932,6 +938,7 @@
     <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1374,7 +1381,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="36" t="inlineStr">
         <is>
@@ -1592,6 +1598,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2873,7 +2886,7 @@
         <v/>
       </c>
       <c r="F34" s="27">
-        <f>SUM(F4:F33)</f>
+        <f>SUMIF(E4:E33,"&gt;0",F4:F33)</f>
         <v/>
       </c>
       <c r="G34" s="28">
@@ -4121,7 +4134,7 @@
         <v/>
       </c>
       <c r="F65" s="27">
-        <f>SUM(F35:F64)</f>
+        <f>SUMIF(E35:E64,"&gt;0",F35:F64)</f>
         <v/>
       </c>
       <c r="G65" s="28">
@@ -5529,7 +5542,7 @@
         <v/>
       </c>
       <c r="F100" s="27">
-        <f>SUM(F66:F99)</f>
+        <f>SUMIF(E66:E99,"&gt;0",F66:F99)</f>
         <v/>
       </c>
       <c r="G100" s="28">
@@ -6617,7 +6630,7 @@
         <v/>
       </c>
       <c r="F127" s="27">
-        <f>SUM(F101:F126)</f>
+        <f>SUMIF(E101:E126,"&gt;0",F101:F126)</f>
         <v/>
       </c>
       <c r="G127" s="28">
@@ -8065,7 +8078,7 @@
         <v/>
       </c>
       <c r="F163" s="27">
-        <f>SUM(F128:F162)</f>
+        <f>SUMIF(E128:E162,"&gt;0",F128:F162)</f>
         <v/>
       </c>
       <c r="G163" s="28">
@@ -9633,7 +9646,7 @@
         <v/>
       </c>
       <c r="F202" s="27">
-        <f>SUM(F164:F201)</f>
+        <f>SUMIF(E164:E201,"&gt;0",F164:F201)</f>
         <v/>
       </c>
       <c r="G202" s="28">
@@ -10761,7 +10774,7 @@
         <v/>
       </c>
       <c r="F230" s="27">
-        <f>SUM(F203:F229)</f>
+        <f>SUMIF(E203:E229,"&gt;0",F203:F229)</f>
         <v/>
       </c>
       <c r="G230" s="28">
@@ -10860,7 +10873,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -10868,7 +10880,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
